--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00896-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00896-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{067A30C7-CBEA-4450-A66B-69D6F11B38D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2014C93A-4993-482E-A014-EB4E39432140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0450CF68-D4E8-48D0-910B-F24A46B10D8F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{826D5F8E-DE14-439F-B462-BF6DDE4AEFFE}"/>
   </bookViews>
   <sheets>
     <sheet name="00896-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1502,25 +1502,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84CBF49-EFA1-408B-937E-72B393D6C02E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A2BE08-D9A8-40D6-9106-E75F1176C585}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1578,7 +1578,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1674,7 +1674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
         <v>53</v>
       </c>
